--- a/output/成绩等级分布.xlsx
+++ b/output/成绩等级分布.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="172" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="427" uniqueCount="8">
   <si>
     <t>TotalScore</t>
   </si>
@@ -728,7 +728,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.21875" customWidth="true"/>
@@ -823,6 +823,126 @@
         <v>2</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="0">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/output/成绩等级分布.xlsx
+++ b/output/成绩等级分布.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="427" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="852" uniqueCount="8">
   <si>
     <t>TotalScore</t>
   </si>
@@ -728,7 +728,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.21875" customWidth="true"/>
@@ -943,6 +943,206 @@
         <v>2</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="0">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/output/成绩等级分布.xlsx
+++ b/output/成绩等级分布.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="852" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="87" uniqueCount="8">
   <si>
     <t>TotalScore</t>
   </si>
@@ -728,11 +728,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.21875" customWidth="true"/>
-    <col min="2" max="2" width="3" customWidth="true"/>
+    <col min="1" max="1" width="5.88671875" customWidth="true"/>
+    <col min="2" max="2" width="5.88671875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -783,366 +783,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B32" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B37" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B42" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B47" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B48" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B50" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="0">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/output/成绩等级分布.xlsx
+++ b/output/成绩等级分布.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="87" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="257" uniqueCount="8">
   <si>
     <t>TotalScore</t>
   </si>
@@ -728,11 +728,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" customWidth="true"/>
-    <col min="2" max="2" width="5.88671875" customWidth="true"/>
+    <col min="1" max="1" width="2.21875" customWidth="true"/>
+    <col min="2" max="2" width="3" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -783,6 +783,86 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="0">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>